--- a/csv/model/market share limits/formula_market share limits_MB.xlsx
+++ b/csv/model/market share limits/formula_market share limits_MB.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="33675" yWindow="3075" windowWidth="17280" windowHeight="8475" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3624" yWindow="2148" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1" iterate="1" calcCompleted="0" calcOnSave="0"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" calcOnSave="0"/>
 </workbook>
 </file>
 
@@ -440,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -592,7 +592,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3292,7 +3292,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5872,7 +5872,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5957,7 +5957,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -6382,7 +6382,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -6627,7 +6627,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6867,7 +6867,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -7107,7 +7107,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
